--- a/demo.xlsx
+++ b/demo.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SJTU\Research\Meta-analysis\Draft\Nature HB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SJTU\Research\Meta-analysis\Draft\Others\Nature HB\Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DD396EB-2CCC-4446-BDD1-7E248B4773F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E34C2E9-4F61-40C4-8FCB-99634D8225F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="600" windowWidth="24800" windowHeight="15400" xr2:uid="{47C3EAF8-CE50-4742-8F81-ECD0AE5EE618}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="2" xr2:uid="{47C3EAF8-CE50-4742-8F81-ECD0AE5EE618}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="effect sizes" sheetId="1" r:id="rId1"/>
+    <sheet name="RoB2.0" sheetId="2" r:id="rId2"/>
+    <sheet name="ROBINS-I" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="87">
   <si>
     <t>Report_ID</t>
   </si>
@@ -243,6 +245,74 @@
   </si>
   <si>
     <t>beverages</t>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>Overall</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low risk</t>
+  </si>
+  <si>
+    <t>Some concerns</t>
+  </si>
+  <si>
+    <t>High risk</t>
+  </si>
+  <si>
+    <t>D4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>Moderate risk</t>
+  </si>
+  <si>
+    <t>Low risk</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -252,7 +322,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="13"/>
       <color theme="1"/>
@@ -300,6 +370,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -326,7 +420,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -341,6 +435,24 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -657,654 +769,699 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2780B6-6123-47F7-ACAE-AE2AB1845101}">
-  <dimension ref="A1:AM12"/>
+  <dimension ref="A1:AO12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>40</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>2021</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>42</v>
       </c>
-      <c r="K2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
         <v>44</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>45</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>43</v>
       </c>
       <c r="AC2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE2" t="s">
         <v>47</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>48</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>49</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>50</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>51</v>
       </c>
-      <c r="AH2" s="2">
+      <c r="AJ2" s="2">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="AI2" s="2">
+      <c r="AK2" s="2">
         <v>6.1600000000000002E-2</v>
       </c>
-      <c r="AJ2" s="2">
+      <c r="AL2" s="2">
         <v>0.24809999999999999</v>
       </c>
-      <c r="AK2" s="2">
+      <c r="AM2" s="2">
         <v>-0.47539999999999999</v>
       </c>
-      <c r="AL2" s="2">
+      <c r="AN2" s="2">
         <v>0.49730000000000002</v>
       </c>
-      <c r="AM2" s="3">
+      <c r="AO2" s="3">
         <v>-0.30738127561787387</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="6">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>40</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>2021</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>42</v>
       </c>
-      <c r="K3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" t="s">
-        <v>43</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" t="s">
+        <v>43</v>
+      </c>
+      <c r="T3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
         <v>44</v>
       </c>
-      <c r="V3" t="s">
+      <c r="X3" t="s">
         <v>45</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
         <v>46</v>
       </c>
-      <c r="Z3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>43</v>
       </c>
       <c r="AC3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" t="s">
         <v>47</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AF3" t="s">
         <v>48</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AG3" t="s">
         <v>52</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AH3" t="s">
         <v>50</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AI3" t="s">
         <v>51</v>
       </c>
-      <c r="AH3" s="2">
+      <c r="AJ3" s="2">
         <v>-1.3205</v>
       </c>
-      <c r="AI3" s="2">
+      <c r="AK3" s="2">
         <v>0.12690000000000001</v>
       </c>
-      <c r="AJ3" s="2">
+      <c r="AL3" s="2">
         <v>0.35620000000000002</v>
       </c>
-      <c r="AK3" s="2">
+      <c r="AM3" s="2">
         <v>-2.0186000000000002</v>
       </c>
-      <c r="AL3" s="2">
+      <c r="AN3" s="2">
         <v>-0.62229999999999996</v>
       </c>
-      <c r="AM3" s="3">
+      <c r="AO3" s="3">
         <v>-0.79209371531842199</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D4" s="6">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>40</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>2021</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>41</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>42</v>
       </c>
-      <c r="K4" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" t="s">
-        <v>43</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
         <v>44</v>
       </c>
-      <c r="V4" t="s">
+      <c r="X4" t="s">
         <v>45</v>
       </c>
-      <c r="W4" t="s">
+      <c r="Y4" t="s">
         <v>46</v>
       </c>
-      <c r="Z4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>43</v>
       </c>
       <c r="AC4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE4" t="s">
         <v>47</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AF4" t="s">
         <v>48</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AG4" t="s">
         <v>53</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AH4" t="s">
         <v>50</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AI4" t="s">
         <v>51</v>
       </c>
-      <c r="AH4" s="2">
+      <c r="AJ4" s="2">
         <v>-0.12559999999999999</v>
       </c>
-      <c r="AI4" s="2">
+      <c r="AK4" s="2">
         <v>0.1026</v>
       </c>
-      <c r="AJ4" s="2">
+      <c r="AL4" s="2">
         <v>0.32040000000000002</v>
       </c>
-      <c r="AK4" s="2">
+      <c r="AM4" s="2">
         <v>-0.75349999999999995</v>
       </c>
-      <c r="AL4" s="2">
+      <c r="AN4" s="2">
         <v>0.50239999999999996</v>
       </c>
-      <c r="AM4" s="3">
+      <c r="AO4" s="3">
         <v>-0.21101390804239023</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>40</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>2021</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>41</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>42</v>
       </c>
-      <c r="K5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R5" t="s">
-        <v>43</v>
-      </c>
-      <c r="U5" t="s">
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" t="s">
+        <v>43</v>
+      </c>
+      <c r="T5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
         <v>44</v>
       </c>
-      <c r="V5" t="s">
+      <c r="X5" t="s">
         <v>45</v>
       </c>
-      <c r="W5" t="s">
+      <c r="Y5" t="s">
         <v>46</v>
       </c>
-      <c r="Z5" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>43</v>
       </c>
       <c r="AC5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE5" t="s">
         <v>47</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AF5" t="s">
         <v>48</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AG5" t="s">
         <v>54</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AH5" t="s">
         <v>50</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AI5" t="s">
         <v>51</v>
       </c>
-      <c r="AH5" s="2">
+      <c r="AJ5" s="2">
         <v>-0.51490000000000002</v>
       </c>
-      <c r="AI5" s="2">
+      <c r="AK5" s="2">
         <v>0.1061</v>
       </c>
-      <c r="AJ5" s="2">
+      <c r="AL5" s="2">
         <v>0.32579999999999998</v>
       </c>
-      <c r="AK5" s="2">
+      <c r="AM5" s="2">
         <v>-1.1534</v>
       </c>
-      <c r="AL5" s="2">
+      <c r="AN5" s="2">
         <v>0.1237</v>
       </c>
-      <c r="AM5" s="3">
+      <c r="AO5" s="3">
         <v>-0.41307713528653672</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6">
+        <v>2.1</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>55</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>56</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>2018</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>41</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>42</v>
       </c>
-      <c r="K6" t="s">
-        <v>43</v>
-      </c>
-      <c r="U6" t="s">
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
         <v>44</v>
       </c>
-      <c r="V6" t="s">
+      <c r="X6" t="s">
         <v>45</v>
       </c>
-      <c r="W6" t="s">
+      <c r="Y6" t="s">
         <v>46</v>
       </c>
-      <c r="Z6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>43</v>
-      </c>
       <c r="AB6" t="s">
         <v>43</v>
       </c>
       <c r="AC6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE6" t="s">
         <v>57</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AF6" t="s">
         <v>48</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AG6" t="s">
         <v>54</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AH6" t="s">
         <v>58</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AI6" t="s">
         <v>51</v>
       </c>
-      <c r="AH6" s="2">
+      <c r="AJ6" s="2">
         <v>-0.30070000000000002</v>
       </c>
-      <c r="AI6" s="2">
+      <c r="AK6" s="2">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="AJ6" s="2">
+      <c r="AL6" s="2">
         <v>0.18970000000000001</v>
       </c>
-      <c r="AK6" s="2">
+      <c r="AM6" s="2">
         <v>-0.67249999999999999</v>
       </c>
-      <c r="AL6" s="2">
+      <c r="AN6" s="2">
         <v>7.1099999999999997E-2</v>
       </c>
-      <c r="AM6" s="3">
+      <c r="AO6" s="3">
         <v>-0.24087967565415419</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6">
+        <v>2.1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
         <v>55</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>56</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>2018</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>41</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>42</v>
       </c>
-      <c r="K7" t="s">
-        <v>43</v>
-      </c>
-      <c r="U7" t="s">
+      <c r="M7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
         <v>44</v>
       </c>
-      <c r="V7" t="s">
+      <c r="X7" t="s">
         <v>45</v>
       </c>
-      <c r="W7" t="s">
+      <c r="Y7" t="s">
         <v>46</v>
       </c>
-      <c r="Z7" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>43</v>
-      </c>
       <c r="AB7" t="s">
         <v>43</v>
       </c>
       <c r="AC7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE7" t="s">
         <v>57</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AF7" t="s">
         <v>48</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AG7" t="s">
         <v>54</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AH7" t="s">
         <v>58</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AI7" t="s">
         <v>51</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>-0.433</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>4.1599999999999998E-2</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>0.2039</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>-0.83250000000000002</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>-3.3399999999999999E-2</v>
       </c>
-      <c r="AM7" s="3">
+      <c r="AO7" s="3">
         <v>-0.24923509468287439</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
         <v>59</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>60</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>2021</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>41</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>42</v>
       </c>
-      <c r="H8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>43</v>
       </c>
       <c r="K8" t="s">
         <v>43</v>
       </c>
-      <c r="N8" t="s">
-        <v>43</v>
-      </c>
-      <c r="O8" t="s">
-        <v>43</v>
-      </c>
-      <c r="U8" t="s">
+      <c r="M8" t="s">
+        <v>43</v>
+      </c>
+      <c r="P8" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>43</v>
+      </c>
+      <c r="W8" t="s">
         <v>44</v>
       </c>
-      <c r="V8" t="s">
+      <c r="X8" t="s">
         <v>61</v>
       </c>
-      <c r="W8" t="s">
+      <c r="Y8" t="s">
         <v>46</v>
       </c>
-      <c r="X8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y8" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="Z8" s="4" t="s">
         <v>62</v>
       </c>
@@ -1314,92 +1471,98 @@
       <c r="AB8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AC8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE8" t="s">
         <v>57</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AF8" t="s">
         <v>48</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AG8" t="s">
         <v>54</v>
       </c>
-      <c r="AF8" t="s">
+      <c r="AH8" t="s">
         <v>63</v>
       </c>
-      <c r="AG8" t="s">
+      <c r="AI8" t="s">
         <v>51</v>
       </c>
-      <c r="AH8" s="2">
+      <c r="AJ8" s="2">
         <v>-0.32050000000000001</v>
       </c>
-      <c r="AI8" s="2">
+      <c r="AK8" s="2">
         <v>3.6400000000000002E-2</v>
       </c>
-      <c r="AJ8" s="2">
+      <c r="AL8" s="2">
         <v>0.1908</v>
       </c>
-      <c r="AK8" s="2">
+      <c r="AM8" s="2">
         <v>-0.69440000000000002</v>
       </c>
-      <c r="AL8" s="2">
+      <c r="AN8" s="2">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>-0.30739527488684848</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="D9" s="6">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
         <v>59</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>60</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>2021</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>41</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>42</v>
       </c>
-      <c r="H9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>43</v>
       </c>
       <c r="K9" t="s">
         <v>43</v>
       </c>
-      <c r="N9" t="s">
-        <v>43</v>
-      </c>
-      <c r="O9" t="s">
-        <v>43</v>
-      </c>
-      <c r="U9" t="s">
+      <c r="M9" t="s">
+        <v>43</v>
+      </c>
+      <c r="P9" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>43</v>
+      </c>
+      <c r="W9" t="s">
         <v>44</v>
       </c>
-      <c r="V9" t="s">
+      <c r="X9" t="s">
         <v>61</v>
       </c>
-      <c r="W9" t="s">
+      <c r="Y9" t="s">
         <v>46</v>
       </c>
-      <c r="X9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y9" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="Z9" s="4" t="s">
         <v>62</v>
       </c>
@@ -1409,92 +1572,98 @@
       <c r="AB9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AC9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE9" t="s">
         <v>57</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AF9" t="s">
         <v>64</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="AG9" t="s">
         <v>54</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AH9" t="s">
         <v>63</v>
       </c>
-      <c r="AG9" t="s">
+      <c r="AI9" t="s">
         <v>51</v>
       </c>
-      <c r="AH9" s="2">
+      <c r="AJ9" s="2">
         <v>-0.1467</v>
       </c>
-      <c r="AI9" s="2">
+      <c r="AK9" s="2">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="AJ9" s="2">
+      <c r="AL9" s="2">
         <v>0.1898</v>
       </c>
-      <c r="AK9" s="2">
+      <c r="AM9" s="2">
         <v>-0.51880000000000004</v>
       </c>
-      <c r="AL9" s="2">
+      <c r="AN9" s="2">
         <v>0.2253</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>-0.18323769254001812</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
       <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="D10" s="6">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>59</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>60</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>2021</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>41</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>42</v>
       </c>
-      <c r="H10" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>43</v>
       </c>
       <c r="K10" t="s">
         <v>43</v>
       </c>
-      <c r="N10" t="s">
-        <v>43</v>
-      </c>
-      <c r="O10" t="s">
-        <v>43</v>
-      </c>
-      <c r="U10" t="s">
+      <c r="M10" t="s">
+        <v>43</v>
+      </c>
+      <c r="P10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>43</v>
+      </c>
+      <c r="W10" t="s">
         <v>44</v>
       </c>
-      <c r="V10" t="s">
+      <c r="X10" t="s">
         <v>61</v>
       </c>
-      <c r="W10" t="s">
+      <c r="Y10" t="s">
         <v>46</v>
       </c>
-      <c r="X10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y10" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="Z10" s="4" t="s">
         <v>62</v>
       </c>
@@ -1504,92 +1673,98 @@
       <c r="AB10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AC10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE10" t="s">
         <v>57</v>
       </c>
-      <c r="AD10" t="s">
+      <c r="AF10" t="s">
         <v>65</v>
       </c>
-      <c r="AE10" t="s">
+      <c r="AG10" t="s">
         <v>54</v>
       </c>
-      <c r="AF10" t="s">
+      <c r="AH10" t="s">
         <v>63</v>
       </c>
-      <c r="AG10" t="s">
+      <c r="AI10" t="s">
         <v>51</v>
       </c>
-      <c r="AH10" s="2">
+      <c r="AJ10" s="2">
         <v>-0.26340000000000002</v>
       </c>
-      <c r="AI10" s="2">
+      <c r="AK10" s="2">
         <v>3.6200000000000003E-2</v>
       </c>
-      <c r="AJ10" s="2">
+      <c r="AL10" s="2">
         <v>0.19040000000000001</v>
       </c>
-      <c r="AK10" s="2">
+      <c r="AM10" s="2">
         <v>-0.63660000000000005</v>
       </c>
-      <c r="AL10" s="2">
+      <c r="AN10" s="2">
         <v>0.10979999999999999</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>-0.25913548404389464</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>3</v>
       </c>
       <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="D11" s="6">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
         <v>59</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>60</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>2021</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>41</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>42</v>
       </c>
-      <c r="H11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>43</v>
       </c>
       <c r="K11" t="s">
         <v>43</v>
       </c>
-      <c r="N11" t="s">
-        <v>43</v>
-      </c>
-      <c r="O11" t="s">
-        <v>43</v>
-      </c>
-      <c r="U11" t="s">
+      <c r="M11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" t="s">
         <v>44</v>
       </c>
-      <c r="V11" t="s">
+      <c r="X11" t="s">
         <v>61</v>
       </c>
-      <c r="W11" t="s">
+      <c r="Y11" t="s">
         <v>46</v>
       </c>
-      <c r="X11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y11" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="Z11" s="4" t="s">
         <v>62</v>
       </c>
@@ -1599,92 +1774,98 @@
       <c r="AB11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AC11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE11" t="s">
         <v>57</v>
       </c>
-      <c r="AD11" t="s">
+      <c r="AF11" t="s">
         <v>66</v>
       </c>
-      <c r="AE11" t="s">
+      <c r="AG11" t="s">
         <v>54</v>
       </c>
-      <c r="AF11" t="s">
+      <c r="AH11" t="s">
         <v>63</v>
       </c>
-      <c r="AG11" t="s">
+      <c r="AI11" t="s">
         <v>51</v>
       </c>
-      <c r="AH11" s="2">
+      <c r="AJ11" s="2">
         <v>-0.27900000000000003</v>
       </c>
-      <c r="AI11" s="2">
+      <c r="AK11" s="2">
         <v>3.6299999999999999E-2</v>
       </c>
-      <c r="AJ11" s="2">
+      <c r="AL11" s="2">
         <v>0.1905</v>
       </c>
-      <c r="AK11" s="2">
+      <c r="AM11" s="2">
         <v>-0.65229999999999999</v>
       </c>
-      <c r="AL11" s="2">
+      <c r="AN11" s="2">
         <v>9.4399999999999998E-2</v>
       </c>
-      <c r="AM11" s="3">
+      <c r="AO11" s="3">
         <v>-0.50821971172574987</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>3</v>
       </c>
       <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="D12" s="6">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
         <v>59</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>60</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>2021</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>41</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>42</v>
       </c>
-      <c r="H12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>43</v>
       </c>
       <c r="K12" t="s">
         <v>43</v>
       </c>
-      <c r="N12" t="s">
-        <v>43</v>
-      </c>
-      <c r="O12" t="s">
-        <v>43</v>
-      </c>
-      <c r="U12" t="s">
+      <c r="M12" t="s">
+        <v>43</v>
+      </c>
+      <c r="P12" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" t="s">
         <v>44</v>
       </c>
-      <c r="V12" t="s">
+      <c r="X12" t="s">
         <v>61</v>
       </c>
-      <c r="W12" t="s">
+      <c r="Y12" t="s">
         <v>46</v>
       </c>
-      <c r="X12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y12" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="Z12" s="4" t="s">
         <v>62</v>
       </c>
@@ -1694,50 +1875,266 @@
       <c r="AB12" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AC12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE12" t="s">
         <v>57</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AF12" t="s">
         <v>67</v>
       </c>
-      <c r="AE12" t="s">
+      <c r="AG12" t="s">
         <v>54</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="AH12" t="s">
         <v>63</v>
       </c>
-      <c r="AG12" t="s">
+      <c r="AI12" t="s">
         <v>51</v>
       </c>
-      <c r="AH12" s="2">
+      <c r="AJ12" s="2">
         <v>-0.22770000000000001</v>
       </c>
-      <c r="AI12" s="2">
+      <c r="AK12" s="2">
         <v>3.6200000000000003E-2</v>
       </c>
-      <c r="AJ12" s="2">
+      <c r="AL12" s="2">
         <v>0.19020000000000001</v>
       </c>
-      <c r="AK12" s="2">
+      <c r="AM12" s="2">
         <v>-0.60040000000000004</v>
       </c>
-      <c r="AL12" s="2">
+      <c r="AN12" s="2">
         <v>0.14510000000000001</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>-0.62743221690590112</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W12" xr:uid="{029A0A45-0ABE-4A95-A5D6-B46139CBAE32}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y12" xr:uid="{029A0A45-0ABE-4A95-A5D6-B46139CBAE32}">
       <formula1>"High Income, Upper-middle Income, Lower-middle Income, Low Income"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG12" xr:uid="{707D2A74-E474-4EE3-AB27-80E0D4D5F427}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AI12" xr:uid="{707D2A74-E474-4EE3-AB27-80E0D4D5F427}">
       <formula1>"Immediate effect, Long term effect"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FEF999C-0339-49E6-AF23-60972240AE12}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:G3" xr:uid="{CBD958E0-C630-4441-B512-8E40C92AA353}">
+      <formula1>"Low risk, Some concerns, High risk"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95DEF6F8-B91D-4F05-983C-036D436B64B1}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.35546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.35546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:E3 H2" xr:uid="{508B0FCC-2226-46C3-A0BB-80B72E5CEC69}">
+      <formula1>"Low risk, Moderate risk, Serious risk, Critical risk, NA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I3" xr:uid="{4483423B-BB95-4FE4-932C-ADAD58F8BD4B}">
+      <formula1>"Low risk, Low risk except for uncontrolled confounding, Moderate risk, Serious risk, Critical risk"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:G3 H3" xr:uid="{E16ADA18-8F6C-412E-B325-A61843BC5312}">
+      <formula1>"Low risk, Some concerns, High risk"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>